--- a/ota-audit/youtube-demand-map.xlsx
+++ b/ota-audit/youtube-demand-map.xlsx
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -14799,7 +14799,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -24643,7 +24643,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -25159,7 +25159,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -25979,7 +25979,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -26187,7 +26187,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -26551,7 +26551,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
@@ -35731,7 +35731,7 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
@@ -36355,7 +36355,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
@@ -36407,7 +36407,7 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
@@ -40091,7 +40091,7 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
@@ -40399,7 +40399,7 @@
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="F778" t="inlineStr">
@@ -41689,7 +41689,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -42052,7 +42052,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -42085,7 +42085,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -42118,7 +42118,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -42250,7 +42250,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>4</v>
@@ -42283,7 +42283,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -42382,7 +42382,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -42448,7 +42448,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -42481,7 +42481,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -42514,7 +42514,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
@@ -42811,7 +42811,7 @@
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -42943,7 +42943,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -43868,7 +43868,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -44052,7 +44052,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -44116,7 +44116,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -44388,7 +44388,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -45532,7 +45532,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -46588,7 +46588,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -47788,7 +47788,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -49064,7 +49064,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>автор, упоминает OTA без метки</t>
+          <t>автор с партнёрской ссылкой OTA</t>
         </is>
       </c>
       <c r="C209" t="n">
